--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I407"/>
+  <dimension ref="A1:I408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13869,6 +13869,39 @@
       <c r="I407" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="C408" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="D408" t="n">
+        <v>380.51</v>
+      </c>
+      <c r="E408" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="F408" t="n">
+        <v>379.86</v>
+      </c>
+      <c r="G408" t="n">
+        <v>386.07</v>
+      </c>
+      <c r="H408" t="n">
+        <v>370.54</v>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -13883,7 +13916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B468"/>
+  <dimension ref="A1:B469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18566,6 +18599,16 @@
       </c>
       <c r="B468" t="n">
         <v>-0.18</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -18734,28 +18777,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2297255878090146</v>
+        <v>0.2281419542246285</v>
       </c>
       <c r="J2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K2" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1334249979900481</v>
+        <v>0.1324026589077006</v>
       </c>
       <c r="M2" t="n">
-        <v>3.643261159650784</v>
+        <v>3.642014466562465</v>
       </c>
       <c r="N2" t="n">
-        <v>19.93026980151174</v>
+        <v>19.9050053967681</v>
       </c>
       <c r="O2" t="n">
-        <v>4.464333074660956</v>
+        <v>4.461502594055965</v>
       </c>
       <c r="P2" t="n">
-        <v>382.6740466800044</v>
+        <v>382.6888742111323</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18812,28 +18855,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1766945954270647</v>
+        <v>0.1749880948814251</v>
       </c>
       <c r="J3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K3" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07645651279642474</v>
+        <v>0.07543811661176392</v>
       </c>
       <c r="M3" t="n">
-        <v>3.668301316082453</v>
+        <v>3.666463923051474</v>
       </c>
       <c r="N3" t="n">
-        <v>21.92880063041131</v>
+        <v>21.90244674011156</v>
       </c>
       <c r="O3" t="n">
-        <v>4.682819730719015</v>
+        <v>4.680004993598998</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1170776583443</v>
+        <v>369.1330555904933</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18890,28 +18933,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06333223766420944</v>
+        <v>0.06329697081492615</v>
       </c>
       <c r="J4" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K4" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02043013587614129</v>
+        <v>0.02053125620554141</v>
       </c>
       <c r="M4" t="n">
-        <v>2.571020639678739</v>
+        <v>2.564870024505195</v>
       </c>
       <c r="N4" t="n">
-        <v>11.18251037127936</v>
+        <v>11.1550466715994</v>
       </c>
       <c r="O4" t="n">
-        <v>3.344026072159032</v>
+        <v>3.339917165379914</v>
       </c>
       <c r="P4" t="n">
-        <v>378.9137721071492</v>
+        <v>378.9141023099882</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18968,28 +19011,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03892493207559205</v>
+        <v>0.03759799376963328</v>
       </c>
       <c r="J5" t="n">
+        <v>407</v>
+      </c>
+      <c r="K5" t="n">
         <v>406</v>
       </c>
-      <c r="K5" t="n">
-        <v>405</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01354238996214863</v>
+        <v>0.01269078108227495</v>
       </c>
       <c r="M5" t="n">
-        <v>1.914863114886397</v>
+        <v>1.9166371952014</v>
       </c>
       <c r="N5" t="n">
-        <v>6.43315191866141</v>
+        <v>6.433994817998848</v>
       </c>
       <c r="O5" t="n">
-        <v>2.536365888167835</v>
+        <v>2.536532045529654</v>
       </c>
       <c r="P5" t="n">
-        <v>381.207804325483</v>
+        <v>381.2202143901908</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19046,28 +19089,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1235506624417157</v>
+        <v>0.1196999391045189</v>
       </c>
       <c r="J6" t="n">
+        <v>407</v>
+      </c>
+      <c r="K6" t="n">
         <v>406</v>
       </c>
-      <c r="K6" t="n">
-        <v>405</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.06276849421965314</v>
+        <v>0.05890056778454045</v>
       </c>
       <c r="M6" t="n">
-        <v>2.891782869690691</v>
+        <v>2.898601477503631</v>
       </c>
       <c r="N6" t="n">
-        <v>13.28557312468623</v>
+        <v>13.3933868488291</v>
       </c>
       <c r="O6" t="n">
-        <v>3.644938013833188</v>
+        <v>3.659697644454949</v>
       </c>
       <c r="P6" t="n">
-        <v>384.2032142777232</v>
+        <v>384.2392278026716</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19124,28 +19167,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1537972805171995</v>
+        <v>0.1496556131578375</v>
       </c>
       <c r="J7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K7" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07129704181583973</v>
+        <v>0.06758405531588962</v>
       </c>
       <c r="M7" t="n">
-        <v>3.334838301744032</v>
+        <v>3.346612153481524</v>
       </c>
       <c r="N7" t="n">
-        <v>17.91546618303729</v>
+        <v>18.0335797387992</v>
       </c>
       <c r="O7" t="n">
-        <v>4.232666557034381</v>
+        <v>4.246596253330331</v>
       </c>
       <c r="P7" t="n">
-        <v>390.1848623415592</v>
+        <v>390.223640694265</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19202,28 +19245,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06159822283549365</v>
+        <v>-0.06833634547265524</v>
       </c>
       <c r="J8" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K8" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005068554059024066</v>
+        <v>0.006207751827045471</v>
       </c>
       <c r="M8" t="n">
-        <v>5.063386402250617</v>
+        <v>5.080483009393122</v>
       </c>
       <c r="N8" t="n">
-        <v>43.30827869034253</v>
+        <v>43.63100704773456</v>
       </c>
       <c r="O8" t="n">
-        <v>6.580902574141524</v>
+        <v>6.605377131378234</v>
       </c>
       <c r="P8" t="n">
-        <v>385.4288986404171</v>
+        <v>385.4919875545011</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19261,7 +19304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I407"/>
+  <dimension ref="A1:I408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38385,6 +38428,53 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>-34.81160972806724,173.3864800327644</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>-34.811098779365814,173.38714370262045</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>-34.81052063372894,173.3876721991115</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>-34.80992072483761,173.3881321482776</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>-34.80929012436164,173.3885656345914</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>-34.80863217953547,173.38884568568054</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-34.80796250024642,173.3891603507545</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I408"/>
+  <dimension ref="A1:I409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13900,6 +13900,39 @@
         <v>370.54</v>
       </c>
       <c r="I408" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>385.45</v>
+      </c>
+      <c r="C409" t="n">
+        <v>372.41</v>
+      </c>
+      <c r="D409" t="n">
+        <v>380.55</v>
+      </c>
+      <c r="E409" t="n">
+        <v>379.12</v>
+      </c>
+      <c r="F409" t="n">
+        <v>380.22</v>
+      </c>
+      <c r="G409" t="n">
+        <v>385.73</v>
+      </c>
+      <c r="H409" t="n">
+        <v>371.01</v>
+      </c>
+      <c r="I409" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -13916,7 +13949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B469"/>
+  <dimension ref="A1:B470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18609,6 +18642,16 @@
       </c>
       <c r="B469" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -18777,28 +18820,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2281419542246285</v>
+        <v>0.2265034844076345</v>
       </c>
       <c r="J2" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K2" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1324026589077006</v>
+        <v>0.131307213169977</v>
       </c>
       <c r="M2" t="n">
-        <v>3.642014466562465</v>
+        <v>3.64110493163843</v>
       </c>
       <c r="N2" t="n">
-        <v>19.9050053967681</v>
+        <v>19.88178388238671</v>
       </c>
       <c r="O2" t="n">
-        <v>4.461502594055965</v>
+        <v>4.458899402586552</v>
       </c>
       <c r="P2" t="n">
-        <v>382.6888742111323</v>
+        <v>382.7042438759292</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18855,28 +18898,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1749880948814251</v>
+        <v>0.1743186062142797</v>
       </c>
       <c r="J3" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K3" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07543811661176392</v>
+        <v>0.07531757386077553</v>
       </c>
       <c r="M3" t="n">
-        <v>3.666463923051474</v>
+        <v>3.660283914142586</v>
       </c>
       <c r="N3" t="n">
-        <v>21.90244674011156</v>
+        <v>21.85303262083337</v>
       </c>
       <c r="O3" t="n">
-        <v>4.680004993598998</v>
+        <v>4.674722731973883</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1330555904933</v>
+        <v>369.1393357283955</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18933,28 +18976,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06329697081492615</v>
+        <v>0.0632822476463647</v>
       </c>
       <c r="J4" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K4" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02053125620554141</v>
+        <v>0.02064552486722315</v>
       </c>
       <c r="M4" t="n">
-        <v>2.564870024505195</v>
+        <v>2.558652598867477</v>
       </c>
       <c r="N4" t="n">
-        <v>11.1550466715994</v>
+        <v>11.12770793524863</v>
       </c>
       <c r="O4" t="n">
-        <v>3.339917165379914</v>
+        <v>3.335821927988457</v>
       </c>
       <c r="P4" t="n">
-        <v>378.9141023099882</v>
+        <v>378.914240420659</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19011,28 +19054,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03759799376963328</v>
+        <v>0.03603516736539168</v>
       </c>
       <c r="J5" t="n">
+        <v>408</v>
+      </c>
+      <c r="K5" t="n">
         <v>407</v>
       </c>
-      <c r="K5" t="n">
-        <v>406</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01269078108227495</v>
+        <v>0.01169863993657305</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9166371952014</v>
+        <v>1.919592654675899</v>
       </c>
       <c r="N5" t="n">
-        <v>6.433994817998848</v>
+        <v>6.441509387960295</v>
       </c>
       <c r="O5" t="n">
-        <v>2.536532045529654</v>
+        <v>2.538012881756177</v>
       </c>
       <c r="P5" t="n">
-        <v>381.2202143901908</v>
+        <v>381.2348580297391</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19089,28 +19132,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1196999391045189</v>
+        <v>0.1160811246991763</v>
       </c>
       <c r="J6" t="n">
+        <v>408</v>
+      </c>
+      <c r="K6" t="n">
         <v>407</v>
       </c>
-      <c r="K6" t="n">
-        <v>406</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.05890056778454045</v>
+        <v>0.0554209506865041</v>
       </c>
       <c r="M6" t="n">
-        <v>2.898601477503631</v>
+        <v>2.904886319857607</v>
       </c>
       <c r="N6" t="n">
-        <v>13.3933868488291</v>
+        <v>13.4855322015323</v>
       </c>
       <c r="O6" t="n">
-        <v>3.659697644454949</v>
+        <v>3.672265268404817</v>
       </c>
       <c r="P6" t="n">
-        <v>384.2392278026716</v>
+        <v>384.2731359920905</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19167,28 +19210,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1496556131578375</v>
+        <v>0.1453970265584346</v>
       </c>
       <c r="J7" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K7" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06758405531588962</v>
+        <v>0.0638304368216227</v>
       </c>
       <c r="M7" t="n">
-        <v>3.346612153481524</v>
+        <v>3.358959433976972</v>
       </c>
       <c r="N7" t="n">
-        <v>18.0335797387992</v>
+        <v>18.16208456519712</v>
       </c>
       <c r="O7" t="n">
-        <v>4.246596253330331</v>
+        <v>4.26169972724465</v>
       </c>
       <c r="P7" t="n">
-        <v>390.223640694265</v>
+        <v>390.2635883624262</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19245,28 +19288,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06833634547265524</v>
+        <v>-0.07474467886379337</v>
       </c>
       <c r="J8" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K8" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006207751827045471</v>
+        <v>0.0073969008006457</v>
       </c>
       <c r="M8" t="n">
-        <v>5.080483009393122</v>
+        <v>5.097396144983313</v>
       </c>
       <c r="N8" t="n">
-        <v>43.63100704773456</v>
+        <v>43.91514647889908</v>
       </c>
       <c r="O8" t="n">
-        <v>6.605377131378234</v>
+        <v>6.626850419233792</v>
       </c>
       <c r="P8" t="n">
-        <v>385.4919875545011</v>
+        <v>385.5521009207084</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19304,7 +19347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I408"/>
+  <dimension ref="A1:I409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38475,6 +38518,53 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>-34.81161047275525,173.38648126879824</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>-34.8110871308338,173.387126865569</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>-34.810520413629824,173.3876718526315</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>-34.80992300371565,173.38813686527874</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>-34.809288678465514,173.38856211058786</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>-34.80863305740613,173.38884924731465</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-34.807961778517395,173.3891552872721</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I409"/>
+  <dimension ref="A1:I412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13935,6 +13935,105 @@
       <c r="I409" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="C410" t="n">
+        <v>367.38</v>
+      </c>
+      <c r="D410" t="n">
+        <v>377.1</v>
+      </c>
+      <c r="E410" t="n">
+        <v>375.54</v>
+      </c>
+      <c r="F410" t="n">
+        <v>377.44</v>
+      </c>
+      <c r="G410" t="n">
+        <v>385.71</v>
+      </c>
+      <c r="H410" t="n">
+        <v>370.91</v>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>380.18</v>
+      </c>
+      <c r="C411" t="n">
+        <v>369.41</v>
+      </c>
+      <c r="D411" t="n">
+        <v>378.14</v>
+      </c>
+      <c r="E411" t="n">
+        <v>376.29</v>
+      </c>
+      <c r="F411" t="n">
+        <v>378.45</v>
+      </c>
+      <c r="G411" t="n">
+        <v>385.82</v>
+      </c>
+      <c r="H411" t="n">
+        <v>370.63</v>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>381.38</v>
+      </c>
+      <c r="C412" t="n">
+        <v>369.82</v>
+      </c>
+      <c r="D412" t="n">
+        <v>378.49</v>
+      </c>
+      <c r="E412" t="n">
+        <v>377.05</v>
+      </c>
+      <c r="F412" t="n">
+        <v>379.28</v>
+      </c>
+      <c r="G412" t="n">
+        <v>386.28</v>
+      </c>
+      <c r="H412" t="n">
+        <v>371.49</v>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -13949,7 +14048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B470"/>
+  <dimension ref="A1:B473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18652,6 +18751,36 @@
       </c>
       <c r="B470" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>-0.22</v>
       </c>
     </row>
   </sheetData>
@@ -18820,28 +18949,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2265034844076345</v>
+        <v>0.2141578106828637</v>
       </c>
       <c r="J2" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K2" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.131307213169977</v>
+        <v>0.1183647772838913</v>
       </c>
       <c r="M2" t="n">
-        <v>3.64110493163843</v>
+        <v>3.675919761091025</v>
       </c>
       <c r="N2" t="n">
-        <v>19.88178388238671</v>
+        <v>20.23067290406473</v>
       </c>
       <c r="O2" t="n">
-        <v>4.458899402586552</v>
+        <v>4.497852032255477</v>
       </c>
       <c r="P2" t="n">
-        <v>382.7042438759292</v>
+        <v>382.8204761341426</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18898,28 +19027,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1743186062142797</v>
+        <v>0.1670734032523663</v>
       </c>
       <c r="J3" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K3" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07531757386077553</v>
+        <v>0.07027246848644919</v>
       </c>
       <c r="M3" t="n">
-        <v>3.660283914142586</v>
+        <v>3.66385542678634</v>
       </c>
       <c r="N3" t="n">
-        <v>21.85303262083337</v>
+        <v>21.87062352075917</v>
       </c>
       <c r="O3" t="n">
-        <v>4.674722731973883</v>
+        <v>4.676603844753068</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1393357283955</v>
+        <v>369.2075418571694</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18976,28 +19105,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0632822476463647</v>
+        <v>0.05930119015798802</v>
       </c>
       <c r="J4" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K4" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02064552486722315</v>
+        <v>0.01841651175973535</v>
       </c>
       <c r="M4" t="n">
-        <v>2.558652598867477</v>
+        <v>2.558681208486052</v>
       </c>
       <c r="N4" t="n">
-        <v>11.12770793524863</v>
+        <v>11.09999371652479</v>
       </c>
       <c r="O4" t="n">
-        <v>3.335821927988457</v>
+        <v>3.331665306798507</v>
       </c>
       <c r="P4" t="n">
-        <v>378.914240420659</v>
+        <v>378.9517177613805</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19054,28 +19183,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03603516736539168</v>
+        <v>0.02726867567438435</v>
       </c>
       <c r="J5" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K5" t="n">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01169863993657305</v>
+        <v>0.006599090959191867</v>
       </c>
       <c r="M5" t="n">
-        <v>1.919592654675899</v>
+        <v>1.950607147006383</v>
       </c>
       <c r="N5" t="n">
-        <v>6.441509387960295</v>
+        <v>6.644874478838269</v>
       </c>
       <c r="O5" t="n">
-        <v>2.538012881756177</v>
+        <v>2.577765404151097</v>
       </c>
       <c r="P5" t="n">
-        <v>381.2348580297391</v>
+        <v>381.3173004579982</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19132,28 +19261,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1160811246991763</v>
+        <v>0.1027785046399341</v>
       </c>
       <c r="J6" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K6" t="n">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0554209506865041</v>
+        <v>0.04298462196900232</v>
       </c>
       <c r="M6" t="n">
-        <v>2.904886319857607</v>
+        <v>2.935181896640274</v>
       </c>
       <c r="N6" t="n">
-        <v>13.4855322015323</v>
+        <v>13.96138951995351</v>
       </c>
       <c r="O6" t="n">
-        <v>3.672265268404817</v>
+        <v>3.736494282071567</v>
       </c>
       <c r="P6" t="n">
-        <v>384.2731359920905</v>
+        <v>384.3982393675485</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19210,28 +19339,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1453970265584346</v>
+        <v>0.1332534938903174</v>
       </c>
       <c r="J7" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K7" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0638304368216227</v>
+        <v>0.05377302612249912</v>
       </c>
       <c r="M7" t="n">
-        <v>3.358959433976972</v>
+        <v>3.393399744499196</v>
       </c>
       <c r="N7" t="n">
-        <v>18.16208456519712</v>
+        <v>18.50393528431428</v>
       </c>
       <c r="O7" t="n">
-        <v>4.26169972724465</v>
+        <v>4.301620076705319</v>
       </c>
       <c r="P7" t="n">
-        <v>390.2635883624262</v>
+        <v>390.3779227492583</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19288,28 +19417,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07474467886379337</v>
+        <v>-0.0934426870050514</v>
       </c>
       <c r="J8" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K8" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0073969008006457</v>
+        <v>0.01143087786513053</v>
       </c>
       <c r="M8" t="n">
-        <v>5.097396144983313</v>
+        <v>5.149022037239679</v>
       </c>
       <c r="N8" t="n">
-        <v>43.91514647889908</v>
+        <v>44.71921151764248</v>
       </c>
       <c r="O8" t="n">
-        <v>6.626850419233792</v>
+        <v>6.687242444957598</v>
       </c>
       <c r="P8" t="n">
-        <v>385.5521009207084</v>
+        <v>385.7281486408392</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19347,7 +19476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I409"/>
+  <dimension ref="A1:I412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38565,6 +38694,147 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>-34.81164164325588,173.3865330056625</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>-34.811116281135824,173.38716900008976</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>-34.81053939717439,173.38770173653757</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>-34.809939320476985,173.38817063901445</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>-34.80929984399408,173.38858932372938</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>-34.80863310904557,173.38884945682253</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>-34.807961932076786,173.3891563646088</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>-34.81163850493005,173.38652779665907</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>-34.81110451670162,173.38715199549827</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>-34.81053367459942,173.3876927280543</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>-34.80993590216185,173.38816356351006</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>-34.80929578745383,173.3885794369397</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>-34.80863282502862,173.38884830452912</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-34.807962362043,173.38915938115147</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-15 22:17:55+00:00</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>-34.81163212189374,173.38651720207696</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>-34.81110214063333,173.38714856107399</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>-34.81053174873269,173.38768969635348</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>-34.80993243826875,173.3881563936662</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-34.809292453860756,173.38857131215286</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-34.808631637321184,173.38884348584776</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-34.807961041432236,173.38915011605613</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I412"/>
+  <dimension ref="A1:I413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14032,6 +14032,39 @@
         <v>371.49</v>
       </c>
       <c r="I412" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>382.78</v>
+      </c>
+      <c r="C413" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="D413" t="n">
+        <v>379.95</v>
+      </c>
+      <c r="E413" t="n">
+        <v>378.79</v>
+      </c>
+      <c r="F413" t="n">
+        <v>381.26</v>
+      </c>
+      <c r="G413" t="n">
+        <v>386.48</v>
+      </c>
+      <c r="H413" t="n">
+        <v>375.52</v>
+      </c>
+      <c r="I413" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14048,7 +14081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B473"/>
+  <dimension ref="A1:B474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18781,6 +18814,16 @@
       </c>
       <c r="B473" t="n">
         <v>-0.22</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -18949,28 +18992,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2141578106828637</v>
+        <v>0.2113202941603451</v>
       </c>
       <c r="J2" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K2" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1183647772838913</v>
+        <v>0.1158313812258617</v>
       </c>
       <c r="M2" t="n">
-        <v>3.675919761091025</v>
+        <v>3.681284483217071</v>
       </c>
       <c r="N2" t="n">
-        <v>20.23067290406473</v>
+        <v>20.26026096619476</v>
       </c>
       <c r="O2" t="n">
-        <v>4.497852032255477</v>
+        <v>4.501139962964356</v>
       </c>
       <c r="P2" t="n">
-        <v>382.8204761341426</v>
+        <v>382.8473177960971</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19027,28 +19070,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1670734032523663</v>
+        <v>0.1667412345508295</v>
       </c>
       <c r="J3" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K3" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07027246848644919</v>
+        <v>0.07040542589859977</v>
       </c>
       <c r="M3" t="n">
-        <v>3.66385542678634</v>
+        <v>3.656344830712659</v>
       </c>
       <c r="N3" t="n">
-        <v>21.87062352075917</v>
+        <v>21.8186178565707</v>
       </c>
       <c r="O3" t="n">
-        <v>4.676603844753068</v>
+        <v>4.671040339856925</v>
       </c>
       <c r="P3" t="n">
-        <v>369.2075418571694</v>
+        <v>369.2106840274185</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19105,28 +19148,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05930119015798802</v>
+        <v>0.05901519344735705</v>
       </c>
       <c r="J4" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K4" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01841651175973535</v>
+        <v>0.01835013858683632</v>
       </c>
       <c r="M4" t="n">
-        <v>2.558681208486052</v>
+        <v>2.553842393681496</v>
       </c>
       <c r="N4" t="n">
-        <v>11.09999371652479</v>
+        <v>11.07385140208551</v>
       </c>
       <c r="O4" t="n">
-        <v>3.331665306798507</v>
+        <v>3.327739683641963</v>
       </c>
       <c r="P4" t="n">
-        <v>378.9517177613805</v>
+        <v>378.9544231648437</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19183,28 +19226,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02726867567438435</v>
+        <v>0.02565619261388374</v>
       </c>
       <c r="J5" t="n">
+        <v>412</v>
+      </c>
+      <c r="K5" t="n">
         <v>411</v>
       </c>
-      <c r="K5" t="n">
-        <v>410</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.006599090959191867</v>
+        <v>0.005859084152746719</v>
       </c>
       <c r="M5" t="n">
-        <v>1.950607147006383</v>
+        <v>1.95430606276546</v>
       </c>
       <c r="N5" t="n">
-        <v>6.644874478838269</v>
+        <v>6.654188748203504</v>
       </c>
       <c r="O5" t="n">
-        <v>2.577765404151097</v>
+        <v>2.579571427234281</v>
       </c>
       <c r="P5" t="n">
-        <v>381.3173004579982</v>
+        <v>381.3325372196616</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19261,28 +19304,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1027785046399341</v>
+        <v>0.09986820682243379</v>
       </c>
       <c r="J6" t="n">
+        <v>412</v>
+      </c>
+      <c r="K6" t="n">
         <v>411</v>
       </c>
-      <c r="K6" t="n">
-        <v>410</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.04298462196900232</v>
+        <v>0.04068702433338656</v>
       </c>
       <c r="M6" t="n">
-        <v>2.935181896640274</v>
+        <v>2.939984872004165</v>
       </c>
       <c r="N6" t="n">
-        <v>13.96138951995351</v>
+        <v>14.01042734266157</v>
       </c>
       <c r="O6" t="n">
-        <v>3.736494282071567</v>
+        <v>3.743050539688392</v>
       </c>
       <c r="P6" t="n">
-        <v>384.3982393675485</v>
+        <v>384.4257395102172</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19339,28 +19382,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1332534938903174</v>
+        <v>0.1295682768638758</v>
       </c>
       <c r="J7" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K7" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05377302612249912</v>
+        <v>0.05093615471444624</v>
       </c>
       <c r="M7" t="n">
-        <v>3.393399744499196</v>
+        <v>3.403383473895008</v>
       </c>
       <c r="N7" t="n">
-        <v>18.50393528431428</v>
+        <v>18.59175551754977</v>
       </c>
       <c r="O7" t="n">
-        <v>4.301620076705319</v>
+        <v>4.311815802831768</v>
       </c>
       <c r="P7" t="n">
-        <v>390.3779227492583</v>
+        <v>390.4127832862342</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19417,28 +19460,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0934426870050514</v>
+        <v>-0.09727887346469948</v>
       </c>
       <c r="J8" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K8" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01143087786513053</v>
+        <v>0.01241166554979622</v>
       </c>
       <c r="M8" t="n">
-        <v>5.149022037239679</v>
+        <v>5.155251797850375</v>
       </c>
       <c r="N8" t="n">
-        <v>44.71921151764248</v>
+        <v>44.75450031119034</v>
       </c>
       <c r="O8" t="n">
-        <v>6.687242444957598</v>
+        <v>6.689880440724658</v>
       </c>
       <c r="P8" t="n">
-        <v>385.7281486408392</v>
+        <v>385.7644372824478</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19476,7 +19519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I412"/>
+  <dimension ref="A1:I413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38835,6 +38878,53 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-16 22:17:45+00:00</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>-34.81162467501685,173.38650484173328</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>-34.81108388547121,173.38712217465005</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>-34.81052371511637,173.38767704983158</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>-34.80992450777505,173.38813997849962</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>-34.80928450143164,173.38855193013393</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>-34.808631120926584,173.38884139076893</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-34.80795485297926,173.38910669939213</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I413"/>
+  <dimension ref="A1:I414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14067,6 +14067,39 @@
       <c r="I413" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>382.63</v>
+      </c>
+      <c r="C414" t="n">
+        <v>373.41</v>
+      </c>
+      <c r="D414" t="n">
+        <v>380.58</v>
+      </c>
+      <c r="E414" t="n">
+        <v>379.53</v>
+      </c>
+      <c r="F414" t="n">
+        <v>382.77</v>
+      </c>
+      <c r="G414" t="n">
+        <v>387.44</v>
+      </c>
+      <c r="H414" t="n">
+        <v>377.06</v>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -14081,7 +14114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B474"/>
+  <dimension ref="A1:B475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18824,6 +18857,16 @@
       </c>
       <c r="B474" t="n">
         <v>0.25</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -18992,28 +19035,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2113202941603451</v>
+        <v>0.2084519565886835</v>
       </c>
       <c r="J2" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K2" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1158313812258617</v>
+        <v>0.1132625669843096</v>
       </c>
       <c r="M2" t="n">
-        <v>3.681284483217071</v>
+        <v>3.687142395903343</v>
       </c>
       <c r="N2" t="n">
-        <v>20.26026096619476</v>
+        <v>20.2924971651657</v>
       </c>
       <c r="O2" t="n">
-        <v>4.501139962964356</v>
+        <v>4.504719432458108</v>
       </c>
       <c r="P2" t="n">
-        <v>382.8473177960971</v>
+        <v>382.8744762544436</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19070,28 +19113,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1667412345508295</v>
+        <v>0.1666293293087876</v>
       </c>
       <c r="J3" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K3" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07040542589859977</v>
+        <v>0.07071171732013859</v>
       </c>
       <c r="M3" t="n">
-        <v>3.656344830712659</v>
+        <v>3.647961807217628</v>
       </c>
       <c r="N3" t="n">
-        <v>21.8186178565707</v>
+        <v>21.76591200791769</v>
       </c>
       <c r="O3" t="n">
-        <v>4.671040339856925</v>
+        <v>4.665395160960933</v>
       </c>
       <c r="P3" t="n">
-        <v>369.2106840274185</v>
+        <v>369.2117435867552</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19148,28 +19191,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05901519344735705</v>
+        <v>0.05904533656654288</v>
       </c>
       <c r="J4" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K4" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01835013858683632</v>
+        <v>0.01847737242303371</v>
       </c>
       <c r="M4" t="n">
-        <v>2.553842393681496</v>
+        <v>2.547807668742103</v>
       </c>
       <c r="N4" t="n">
-        <v>11.07385140208551</v>
+        <v>11.04704718029284</v>
       </c>
       <c r="O4" t="n">
-        <v>3.327739683641963</v>
+        <v>3.323709852001651</v>
       </c>
       <c r="P4" t="n">
-        <v>378.9544231648437</v>
+        <v>378.9541377588807</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19226,28 +19269,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02565619261388374</v>
+        <v>0.02443193755545527</v>
       </c>
       <c r="J5" t="n">
+        <v>413</v>
+      </c>
+      <c r="K5" t="n">
         <v>412</v>
       </c>
-      <c r="K5" t="n">
-        <v>411</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.005859084152746719</v>
+        <v>0.005336199838185673</v>
       </c>
       <c r="M5" t="n">
-        <v>1.95430606276546</v>
+        <v>1.956104211019633</v>
       </c>
       <c r="N5" t="n">
-        <v>6.654188748203504</v>
+        <v>6.652887690706971</v>
       </c>
       <c r="O5" t="n">
-        <v>2.579571427234281</v>
+        <v>2.579319230089012</v>
       </c>
       <c r="P5" t="n">
-        <v>381.3325372196616</v>
+        <v>381.3441163204387</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19304,28 +19347,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09986820682243379</v>
+        <v>0.09774699683574656</v>
       </c>
       <c r="J6" t="n">
+        <v>413</v>
+      </c>
+      <c r="K6" t="n">
         <v>412</v>
       </c>
-      <c r="K6" t="n">
-        <v>411</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.04068702433338656</v>
+        <v>0.03915015284036849</v>
       </c>
       <c r="M6" t="n">
-        <v>2.939984872004165</v>
+        <v>2.941684128913543</v>
       </c>
       <c r="N6" t="n">
-        <v>14.01042734266157</v>
+        <v>14.02100212540752</v>
       </c>
       <c r="O6" t="n">
-        <v>3.743050539688392</v>
+        <v>3.744462862068139</v>
       </c>
       <c r="P6" t="n">
-        <v>384.4257395102172</v>
+        <v>384.4458020813591</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19382,28 +19425,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1295682768638758</v>
+        <v>0.1264105569277417</v>
       </c>
       <c r="J7" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K7" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05093615471444624</v>
+        <v>0.048636208927061</v>
       </c>
       <c r="M7" t="n">
-        <v>3.403383473895008</v>
+        <v>3.410906393298869</v>
       </c>
       <c r="N7" t="n">
-        <v>18.59175551754977</v>
+        <v>18.64526208292386</v>
       </c>
       <c r="O7" t="n">
-        <v>4.311815802831768</v>
+        <v>4.318015989192706</v>
       </c>
       <c r="P7" t="n">
-        <v>390.4127832862342</v>
+        <v>390.4426817215518</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19460,28 +19503,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09727887346469948</v>
+        <v>-0.1002972975021921</v>
       </c>
       <c r="J8" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K8" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01241166554979622</v>
+        <v>0.0132357357845464</v>
       </c>
       <c r="M8" t="n">
-        <v>5.155251797850375</v>
+        <v>5.157440497902722</v>
       </c>
       <c r="N8" t="n">
-        <v>44.75450031119034</v>
+        <v>44.73615830004187</v>
       </c>
       <c r="O8" t="n">
-        <v>6.689880440724658</v>
+        <v>6.688509422886527</v>
       </c>
       <c r="P8" t="n">
-        <v>385.7644372824478</v>
+        <v>385.7930168137779</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19519,7 +19562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I413"/>
+  <dimension ref="A1:I414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38925,6 +38968,53 @@
         </is>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>-34.81162547289659,173.3865061660557</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>-34.81108133554333,173.38711848892825</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>-34.8105202485555,173.38767159277154</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>-34.809921135035665,173.38813299733778</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>-34.809278436698264,173.38853714889973</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>-34.80862864223202,173.38883133439094</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-34.80795248815691,173.38909010841053</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I414"/>
+  <dimension ref="A1:I415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14100,6 +14100,39 @@
       <c r="I414" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>384.6</v>
+      </c>
+      <c r="C415" t="n">
+        <v>377.13</v>
+      </c>
+      <c r="D415" t="n">
+        <v>382.12</v>
+      </c>
+      <c r="E415" t="n">
+        <v>380.58</v>
+      </c>
+      <c r="F415" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="G415" t="n">
+        <v>388.13</v>
+      </c>
+      <c r="H415" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B475"/>
+  <dimension ref="A1:B476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18867,6 +18900,16 @@
       </c>
       <c r="B475" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -19035,28 +19078,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2084519565886835</v>
+        <v>0.2065556438824249</v>
       </c>
       <c r="J2" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K2" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1132625669843096</v>
+        <v>0.1118732361503573</v>
       </c>
       <c r="M2" t="n">
-        <v>3.687142395903343</v>
+        <v>3.687890748626767</v>
       </c>
       <c r="N2" t="n">
-        <v>20.2924971651657</v>
+        <v>20.27864000098478</v>
       </c>
       <c r="O2" t="n">
-        <v>4.504719432458108</v>
+        <v>4.503181097955619</v>
       </c>
       <c r="P2" t="n">
-        <v>382.8744762544436</v>
+        <v>382.8925473612841</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19113,28 +19156,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1666293293087876</v>
+        <v>0.1683506867313971</v>
       </c>
       <c r="J3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K3" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07071171732013859</v>
+        <v>0.07239416397944398</v>
       </c>
       <c r="M3" t="n">
-        <v>3.647961807217628</v>
+        <v>3.648815212319659</v>
       </c>
       <c r="N3" t="n">
-        <v>21.76591200791769</v>
+        <v>21.74230763539232</v>
       </c>
       <c r="O3" t="n">
-        <v>4.665395160960933</v>
+        <v>4.662864745560642</v>
       </c>
       <c r="P3" t="n">
-        <v>369.2117435867552</v>
+        <v>369.1953397342722</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19191,28 +19234,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05904533656654288</v>
+        <v>0.05983161836690648</v>
       </c>
       <c r="J4" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K4" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01847737242303371</v>
+        <v>0.01906701523031351</v>
       </c>
       <c r="M4" t="n">
-        <v>2.547807668742103</v>
+        <v>2.545557315912776</v>
       </c>
       <c r="N4" t="n">
-        <v>11.04704718029284</v>
+        <v>11.02640808688389</v>
       </c>
       <c r="O4" t="n">
-        <v>3.323709852001651</v>
+        <v>3.320603572678301</v>
       </c>
       <c r="P4" t="n">
-        <v>378.9541377588807</v>
+        <v>378.9466448056487</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19269,28 +19312,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02443193755545527</v>
+        <v>0.02372979295919225</v>
       </c>
       <c r="J5" t="n">
+        <v>414</v>
+      </c>
+      <c r="K5" t="n">
         <v>413</v>
       </c>
-      <c r="K5" t="n">
-        <v>412</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.005336199838185673</v>
+        <v>0.005062416751364318</v>
       </c>
       <c r="M5" t="n">
-        <v>1.956104211019633</v>
+        <v>1.955063819602509</v>
       </c>
       <c r="N5" t="n">
-        <v>6.652887690706971</v>
+        <v>6.641612391944892</v>
       </c>
       <c r="O5" t="n">
-        <v>2.579319230089012</v>
+        <v>2.577132591068005</v>
       </c>
       <c r="P5" t="n">
-        <v>381.3441163204387</v>
+        <v>381.3508003789622</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19347,28 +19390,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09774699683574656</v>
+        <v>0.09659921112325692</v>
       </c>
       <c r="J6" t="n">
+        <v>414</v>
+      </c>
+      <c r="K6" t="n">
         <v>413</v>
       </c>
-      <c r="K6" t="n">
-        <v>412</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03915015284036849</v>
+        <v>0.03846220172113424</v>
       </c>
       <c r="M6" t="n">
-        <v>2.941684128913543</v>
+        <v>2.939349494340573</v>
       </c>
       <c r="N6" t="n">
-        <v>14.02100212540752</v>
+        <v>13.99996873422696</v>
       </c>
       <c r="O6" t="n">
-        <v>3.744462862068139</v>
+        <v>3.741653208706943</v>
       </c>
       <c r="P6" t="n">
-        <v>384.4458020813591</v>
+        <v>384.4567284160706</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19425,28 +19468,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1264105569277417</v>
+        <v>0.1235993484533186</v>
       </c>
       <c r="J7" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K7" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L7" t="n">
-        <v>0.048636208927061</v>
+        <v>0.04668385091702876</v>
       </c>
       <c r="M7" t="n">
-        <v>3.410906393298869</v>
+        <v>3.416591680105062</v>
       </c>
       <c r="N7" t="n">
-        <v>18.64526208292386</v>
+        <v>18.67749272469357</v>
       </c>
       <c r="O7" t="n">
-        <v>4.318015989192706</v>
+        <v>4.32174649010022</v>
       </c>
       <c r="P7" t="n">
-        <v>390.4426817215518</v>
+        <v>390.4694714216497</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19503,28 +19546,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1002972975021921</v>
+        <v>-0.1031492434220278</v>
       </c>
       <c r="J8" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K8" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0132357357845464</v>
+        <v>0.01404824632083679</v>
       </c>
       <c r="M8" t="n">
-        <v>5.157440497902722</v>
+        <v>5.158624938679669</v>
       </c>
       <c r="N8" t="n">
-        <v>44.73615830004187</v>
+        <v>44.70762305803548</v>
       </c>
       <c r="O8" t="n">
-        <v>6.688509422886527</v>
+        <v>6.686375928560664</v>
       </c>
       <c r="P8" t="n">
-        <v>385.7930168137779</v>
+        <v>385.8201947255489</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19562,7 +19605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I414"/>
+  <dimension ref="A1:I415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39015,6 +39058,53 @@
         </is>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>-34.811614994074986,173.38648877328978</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>-34.811059777057665,173.38708732783493</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>-34.810511774738956,173.3876582532933</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>-34.80991634939125,173.38812309163615</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>-34.80927056459129,173.3885179626652</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-34.808626860669776,173.38882410636964</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-34.807952042832945,173.38908698413488</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I415"/>
+  <dimension ref="A1:I417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14133,6 +14133,72 @@
       <c r="I415" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>385.35</v>
+      </c>
+      <c r="C416" t="n">
+        <v>376.58</v>
+      </c>
+      <c r="D416" t="n">
+        <v>382.88</v>
+      </c>
+      <c r="E416" t="n">
+        <v>380.98</v>
+      </c>
+      <c r="F416" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="G416" t="n">
+        <v>388.74</v>
+      </c>
+      <c r="H416" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>387.24</v>
+      </c>
+      <c r="C417" t="n">
+        <v>376.82</v>
+      </c>
+      <c r="D417" t="n">
+        <v>384.03</v>
+      </c>
+      <c r="E417" t="n">
+        <v>381.94</v>
+      </c>
+      <c r="F417" t="n">
+        <v>387.38</v>
+      </c>
+      <c r="G417" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="H417" t="n">
+        <v>377.9</v>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -14147,7 +14213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B476"/>
+  <dimension ref="A1:B478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18910,6 +18976,26 @@
       </c>
       <c r="B476" t="n">
         <v>0.79</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>
@@ -19078,28 +19164,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2065556438824249</v>
+        <v>0.2044873241800278</v>
       </c>
       <c r="J2" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K2" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1118732361503573</v>
+        <v>0.1109532495791085</v>
       </c>
       <c r="M2" t="n">
-        <v>3.687890748626767</v>
+        <v>3.680654868722627</v>
       </c>
       <c r="N2" t="n">
-        <v>20.27864000098478</v>
+        <v>20.20665072481599</v>
       </c>
       <c r="O2" t="n">
-        <v>4.503181097955619</v>
+        <v>4.495180833383235</v>
       </c>
       <c r="P2" t="n">
-        <v>382.8925473612841</v>
+        <v>382.9122854402409</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19156,28 +19242,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1683506867313971</v>
+        <v>0.1712857916574436</v>
       </c>
       <c r="J3" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K3" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07239416397944398</v>
+        <v>0.07545337284003895</v>
       </c>
       <c r="M3" t="n">
-        <v>3.648815212319659</v>
+        <v>3.647644976182475</v>
       </c>
       <c r="N3" t="n">
-        <v>21.74230763539232</v>
+        <v>21.6805261323435</v>
       </c>
       <c r="O3" t="n">
-        <v>4.662864745560642</v>
+        <v>4.65623518868447</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1953397342722</v>
+        <v>369.1673173545212</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19234,28 +19320,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05983161836690648</v>
+        <v>0.06267767860149248</v>
       </c>
       <c r="J4" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K4" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01906701523031351</v>
+        <v>0.02105586493384948</v>
       </c>
       <c r="M4" t="n">
-        <v>2.545557315912776</v>
+        <v>2.547572355533037</v>
       </c>
       <c r="N4" t="n">
-        <v>11.02640808688389</v>
+        <v>11.01507876527144</v>
       </c>
       <c r="O4" t="n">
-        <v>3.320603572678301</v>
+        <v>3.318897221257604</v>
       </c>
       <c r="P4" t="n">
-        <v>378.9466448056487</v>
+        <v>378.9194686408249</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19312,28 +19398,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02372979295919225</v>
+        <v>0.02321768452321153</v>
       </c>
       <c r="J5" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K5" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005062416751364318</v>
+        <v>0.004904215532941736</v>
       </c>
       <c r="M5" t="n">
-        <v>1.955063819602509</v>
+        <v>1.948319318811678</v>
       </c>
       <c r="N5" t="n">
-        <v>6.641612391944892</v>
+        <v>6.612030887094697</v>
       </c>
       <c r="O5" t="n">
-        <v>2.577132591068005</v>
+        <v>2.571386957868204</v>
       </c>
       <c r="P5" t="n">
-        <v>381.3508003789622</v>
+        <v>381.3556801555508</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19390,28 +19476,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09659921112325692</v>
+        <v>0.09609653045797865</v>
       </c>
       <c r="J6" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K6" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03846220172113424</v>
+        <v>0.03851088896703614</v>
       </c>
       <c r="M6" t="n">
-        <v>2.939349494340573</v>
+        <v>2.928939566932767</v>
       </c>
       <c r="N6" t="n">
-        <v>13.99996873422696</v>
+        <v>13.93727811024081</v>
       </c>
       <c r="O6" t="n">
-        <v>3.741653208706943</v>
+        <v>3.733266412974142</v>
       </c>
       <c r="P6" t="n">
-        <v>384.4567284160706</v>
+        <v>384.461515072674</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19468,28 +19554,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1235993484533186</v>
+        <v>0.1189819074683393</v>
       </c>
       <c r="J7" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K7" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04668385091702876</v>
+        <v>0.04367629537882434</v>
       </c>
       <c r="M7" t="n">
-        <v>3.416591680105062</v>
+        <v>3.422842179167196</v>
       </c>
       <c r="N7" t="n">
-        <v>18.67749272469357</v>
+        <v>18.69381578355781</v>
       </c>
       <c r="O7" t="n">
-        <v>4.32174649010022</v>
+        <v>4.323634557124111</v>
       </c>
       <c r="P7" t="n">
-        <v>390.4694714216497</v>
+        <v>390.5135513511791</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19546,28 +19632,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1031492434220278</v>
+        <v>-0.1082373403666763</v>
       </c>
       <c r="J8" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="K8" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01404824632083679</v>
+        <v>0.01558724562788893</v>
       </c>
       <c r="M8" t="n">
-        <v>5.158624938679669</v>
+        <v>5.158320485404941</v>
       </c>
       <c r="N8" t="n">
-        <v>44.70762305803548</v>
+        <v>44.6209749369154</v>
       </c>
       <c r="O8" t="n">
-        <v>6.686375928560664</v>
+        <v>6.679893332749812</v>
       </c>
       <c r="P8" t="n">
-        <v>385.8201947255489</v>
+        <v>385.8687702209431</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19605,7 +19691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I415"/>
+  <dimension ref="A1:I417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39105,6 +39191,100 @@
         </is>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-34.81161100467524,173.38648215167953</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>-34.81106296446869,173.38709193498482</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>-34.81050759285491,173.3876516701752</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>-34.80991452628841,173.38811931803582</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>-34.80926678919195,173.38850876110502</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-34.808625285665116,173.38881771638006</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-34.80795133645688,173.38908202838738</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>-34.811600951386254,173.38646546522457</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>-34.811061573598444,173.3870899245921</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>-34.81050126500338,173.3876417088793</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-34.80991015084108,173.3881102613957</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>-34.80925992117648,173.38849202209875</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-34.80862371066012,173.38881132639068</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-34.80795119825284,173.3890810587846</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0022/nzd0022.xlsx
+++ b/data/nzd0022/nzd0022.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I417"/>
+  <dimension ref="A1:I419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14199,6 +14199,72 @@
       <c r="I417" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>388.07</v>
+      </c>
+      <c r="C418" t="n">
+        <v>375.81</v>
+      </c>
+      <c r="D418" t="n">
+        <v>386.17</v>
+      </c>
+      <c r="E418" t="n">
+        <v>384.27</v>
+      </c>
+      <c r="F418" t="n">
+        <v>388.17</v>
+      </c>
+      <c r="G418" t="n">
+        <v>391.35</v>
+      </c>
+      <c r="H418" t="n">
+        <v>378.35</v>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>388.98</v>
+      </c>
+      <c r="C419" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="D419" t="n">
+        <v>387.31</v>
+      </c>
+      <c r="E419" t="n">
+        <v>384.35</v>
+      </c>
+      <c r="F419" t="n">
+        <v>388.06</v>
+      </c>
+      <c r="G419" t="n">
+        <v>390.01</v>
+      </c>
+      <c r="H419" t="n">
+        <v>376.91</v>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -14213,7 +14279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B478"/>
+  <dimension ref="A1:B480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18996,6 +19062,26 @@
       </c>
       <c r="B478" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -19164,28 +19250,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2044873241800278</v>
+        <v>0.204609636195829</v>
       </c>
       <c r="J2" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K2" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1109532495791085</v>
+        <v>0.1122595716489393</v>
       </c>
       <c r="M2" t="n">
-        <v>3.680654868722627</v>
+        <v>3.66519843414902</v>
       </c>
       <c r="N2" t="n">
-        <v>20.20665072481599</v>
+        <v>20.11103197019658</v>
       </c>
       <c r="O2" t="n">
-        <v>4.495180833383235</v>
+        <v>4.484532525269114</v>
       </c>
       <c r="P2" t="n">
-        <v>382.9122854402409</v>
+        <v>382.9111106802474</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19242,28 +19328,28 @@
         <v>0.0684</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1712857916574436</v>
+        <v>0.1740130193518623</v>
       </c>
       <c r="J3" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K3" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07545337284003895</v>
+        <v>0.07841920908406974</v>
       </c>
       <c r="M3" t="n">
-        <v>3.647644976182475</v>
+        <v>3.64532905266828</v>
       </c>
       <c r="N3" t="n">
-        <v>21.6805261323435</v>
+        <v>21.61692987788247</v>
       </c>
       <c r="O3" t="n">
-        <v>4.65623518868447</v>
+        <v>4.649401023560182</v>
       </c>
       <c r="P3" t="n">
-        <v>369.1673173545212</v>
+        <v>369.1411683060358</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19320,28 +19406,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06267767860149248</v>
+        <v>0.06862223332297311</v>
       </c>
       <c r="J4" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K4" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02105586493384948</v>
+        <v>0.02503260094069082</v>
       </c>
       <c r="M4" t="n">
-        <v>2.547572355533037</v>
+        <v>2.565873902361032</v>
       </c>
       <c r="N4" t="n">
-        <v>11.01507876527144</v>
+        <v>11.14123632782426</v>
       </c>
       <c r="O4" t="n">
-        <v>3.318897221257604</v>
+        <v>3.337849057076167</v>
       </c>
       <c r="P4" t="n">
-        <v>378.9194686408249</v>
+        <v>378.8624767083941</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19398,28 +19484,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02321768452321153</v>
+        <v>0.02547181286998362</v>
       </c>
       <c r="J5" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K5" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004904215532941736</v>
+        <v>0.005944781848045588</v>
       </c>
       <c r="M5" t="n">
-        <v>1.948319318811678</v>
+        <v>1.949324115153063</v>
       </c>
       <c r="N5" t="n">
-        <v>6.612030887094697</v>
+        <v>6.605893881162694</v>
       </c>
       <c r="O5" t="n">
-        <v>2.571386957868204</v>
+        <v>2.570193354820351</v>
       </c>
       <c r="P5" t="n">
-        <v>381.3556801555508</v>
+        <v>381.3340925406123</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19476,28 +19562,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09609653045797865</v>
+        <v>0.09713824659119592</v>
       </c>
       <c r="J6" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K6" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03851088896703614</v>
+        <v>0.0397591007309287</v>
       </c>
       <c r="M6" t="n">
-        <v>2.928939566932767</v>
+        <v>2.920709522312086</v>
       </c>
       <c r="N6" t="n">
-        <v>13.93727811024081</v>
+        <v>13.87590958137817</v>
       </c>
       <c r="O6" t="n">
-        <v>3.733266412974142</v>
+        <v>3.72503819864685</v>
       </c>
       <c r="P6" t="n">
-        <v>384.461515072674</v>
+        <v>384.4515390030206</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19554,28 +19640,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1189819074683393</v>
+        <v>0.1160519579987899</v>
       </c>
       <c r="J7" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K7" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04367629537882434</v>
+        <v>0.04202514953963588</v>
       </c>
       <c r="M7" t="n">
-        <v>3.422842179167196</v>
+        <v>3.420659722887504</v>
       </c>
       <c r="N7" t="n">
-        <v>18.69381578355781</v>
+        <v>18.64959293826699</v>
       </c>
       <c r="O7" t="n">
-        <v>4.323634557124111</v>
+        <v>4.318517446794327</v>
       </c>
       <c r="P7" t="n">
-        <v>390.5135513511791</v>
+        <v>390.5416433824174</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19632,28 +19718,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1082373403666763</v>
+        <v>-0.1134035405065475</v>
       </c>
       <c r="J8" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K8" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01558724562788893</v>
+        <v>0.0172359227976604</v>
       </c>
       <c r="M8" t="n">
-        <v>5.158320485404941</v>
+        <v>5.158616292807838</v>
       </c>
       <c r="N8" t="n">
-        <v>44.6209749369154</v>
+        <v>44.54382761491742</v>
       </c>
       <c r="O8" t="n">
-        <v>6.679893332749812</v>
+        <v>6.674116242238925</v>
       </c>
       <c r="P8" t="n">
-        <v>385.8687702209431</v>
+        <v>385.918300925764</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19691,7 +19777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I417"/>
+  <dimension ref="A1:I419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39285,6 +39371,100 @@
         </is>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>-34.81159653644908,173.38645813731176</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>-34.81106742684383,173.38709838499523</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>-34.81048948969483,173.38762317221097</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-34.809899531262964,173.38808828017937</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>-34.809256748232876,173.38848428887457</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-34.80861854670694,173.38879037560764</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-34.80795050723252,173.3890762107708</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>-34.811591695975274,173.386450103095</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>-34.8110585020932,173.3870854849751</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>-34.81048321686573,173.38761329753933</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>-34.80989916664219,173.3880875254596</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-34.80925719003518,173.38848536565257</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-34.80862200655597,173.388804412632</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-34.807952718496836,173.38909172441518</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
